--- a/Daftar Nilai Paket B.xlsx
+++ b/Daftar Nilai Paket B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\Laporan PKBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{295D1137-68F7-410F-98B4-5BFF02D1A1D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF27855F-2552-498C-A78E-08703C51C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -507,16 +507,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -1041,40 +1041,40 @@
       <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
     </row>
     <row r="3" spans="1:14" ht="24.95" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
     </row>
     <row r="4" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14" ht="24.95" customHeight="1"/>
@@ -1150,11 +1150,21 @@
       <c r="I7" s="11">
         <v>45</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="11"/>
-      <c r="N7" s="11"/>
+      <c r="J7" s="11">
+        <v>85</v>
+      </c>
+      <c r="K7" s="11">
+        <v>70</v>
+      </c>
+      <c r="L7" s="11">
+        <v>38</v>
+      </c>
+      <c r="M7" s="11">
+        <v>38</v>
+      </c>
+      <c r="N7" s="11">
+        <v>82</v>
+      </c>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A8" s="10">
@@ -1184,11 +1194,21 @@
       <c r="I8" s="11">
         <v>31</v>
       </c>
-      <c r="J8" s="11"/>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11"/>
+      <c r="J8" s="11">
+        <v>93</v>
+      </c>
+      <c r="K8" s="11">
+        <v>65</v>
+      </c>
+      <c r="L8" s="11">
+        <v>36</v>
+      </c>
+      <c r="M8" s="11">
+        <v>36</v>
+      </c>
+      <c r="N8" s="11">
+        <v>80</v>
+      </c>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A9" s="10">
@@ -1204,7 +1224,7 @@
         <v>53</v>
       </c>
       <c r="E9" s="11">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="F9" s="11">
         <v>70</v>
@@ -1218,11 +1238,21 @@
       <c r="I9" s="11">
         <v>34</v>
       </c>
-      <c r="J9" s="11"/>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="11"/>
+      <c r="J9" s="11">
+        <v>93</v>
+      </c>
+      <c r="K9" s="11">
+        <v>68</v>
+      </c>
+      <c r="L9" s="11">
+        <v>46</v>
+      </c>
+      <c r="M9" s="11">
+        <v>46</v>
+      </c>
+      <c r="N9" s="11">
+        <v>78</v>
+      </c>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A10" s="10">
@@ -1238,7 +1268,7 @@
         <v>40</v>
       </c>
       <c r="E10" s="11">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="F10" s="11">
         <v>65</v>
@@ -1252,11 +1282,21 @@
       <c r="I10" s="11">
         <v>35</v>
       </c>
-      <c r="J10" s="11"/>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="11"/>
+      <c r="J10" s="11">
+        <v>90</v>
+      </c>
+      <c r="K10" s="11">
+        <v>80</v>
+      </c>
+      <c r="L10" s="11">
+        <v>46</v>
+      </c>
+      <c r="M10" s="11">
+        <v>46</v>
+      </c>
+      <c r="N10" s="11">
+        <v>84</v>
+      </c>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A11" s="10">
@@ -1275,10 +1315,10 @@
         <v>45</v>
       </c>
       <c r="F11" s="11">
-        <v>67.5</v>
+        <v>68</v>
       </c>
       <c r="G11" s="11">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H11" s="11">
         <v>25</v>
@@ -1286,11 +1326,21 @@
       <c r="I11" s="11">
         <v>36</v>
       </c>
-      <c r="J11" s="11"/>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="11"/>
+      <c r="J11" s="11">
+        <v>93</v>
+      </c>
+      <c r="K11" s="11">
+        <v>73</v>
+      </c>
+      <c r="L11" s="11">
+        <v>40</v>
+      </c>
+      <c r="M11" s="11">
+        <v>40</v>
+      </c>
+      <c r="N11" s="11">
+        <v>84</v>
+      </c>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A12" s="10">
@@ -1320,11 +1370,21 @@
       <c r="I12" s="11">
         <v>35</v>
       </c>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
+      <c r="J12" s="11">
+        <v>88</v>
+      </c>
+      <c r="K12" s="11">
+        <v>55</v>
+      </c>
+      <c r="L12" s="11">
+        <v>30</v>
+      </c>
+      <c r="M12" s="11">
+        <v>30</v>
+      </c>
+      <c r="N12" s="11">
+        <v>78</v>
+      </c>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A13" s="10">
@@ -1340,10 +1400,10 @@
         <v>25</v>
       </c>
       <c r="E13" s="11">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="F13" s="11">
-        <v>37.5</v>
+        <v>38</v>
       </c>
       <c r="G13" s="11">
         <v>23</v>
@@ -1354,11 +1414,21 @@
       <c r="I13" s="11">
         <v>34</v>
       </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
+      <c r="J13" s="11">
+        <v>80</v>
+      </c>
+      <c r="K13" s="11">
+        <v>43</v>
+      </c>
+      <c r="L13" s="11">
+        <v>40</v>
+      </c>
+      <c r="M13" s="11">
+        <v>40</v>
+      </c>
+      <c r="N13" s="11">
+        <v>48</v>
+      </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A14" s="10">
@@ -1388,11 +1458,21 @@
       <c r="I14" s="11">
         <v>48</v>
       </c>
-      <c r="J14" s="11"/>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="11"/>
+      <c r="J14" s="11">
+        <v>88</v>
+      </c>
+      <c r="K14" s="11">
+        <v>73</v>
+      </c>
+      <c r="L14" s="11">
+        <v>38</v>
+      </c>
+      <c r="M14" s="11">
+        <v>38</v>
+      </c>
+      <c r="N14" s="11">
+        <v>80</v>
+      </c>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A15" s="10">
@@ -1408,7 +1488,7 @@
         <v>38</v>
       </c>
       <c r="E15" s="11">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="F15" s="11">
         <v>70</v>
@@ -1422,11 +1502,21 @@
       <c r="I15" s="11">
         <v>35</v>
       </c>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
+      <c r="J15" s="11">
+        <v>93</v>
+      </c>
+      <c r="K15" s="11">
+        <v>63</v>
+      </c>
+      <c r="L15" s="11">
+        <v>38</v>
+      </c>
+      <c r="M15" s="11">
+        <v>38</v>
+      </c>
+      <c r="N15" s="11">
+        <v>78</v>
+      </c>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A16" s="10">
@@ -1442,10 +1532,10 @@
         <v>38</v>
       </c>
       <c r="E16" s="11">
-        <v>42.5</v>
+        <v>43</v>
       </c>
       <c r="F16" s="11">
-        <v>92.5</v>
+        <v>93</v>
       </c>
       <c r="G16" s="11">
         <v>36</v>
@@ -1456,11 +1546,21 @@
       <c r="I16" s="11">
         <v>35</v>
       </c>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="J16" s="11">
+        <v>90</v>
+      </c>
+      <c r="K16" s="11">
+        <v>43</v>
+      </c>
+      <c r="L16" s="11">
+        <v>48</v>
+      </c>
+      <c r="M16" s="11">
+        <v>48</v>
+      </c>
+      <c r="N16" s="11">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A17" s="10">
@@ -1476,7 +1576,7 @@
         <v>28</v>
       </c>
       <c r="E17" s="11">
-        <v>42.5</v>
+        <v>43</v>
       </c>
       <c r="F17" s="11">
         <v>50</v>
@@ -1490,11 +1590,21 @@
       <c r="I17" s="11">
         <v>36</v>
       </c>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
+      <c r="J17" s="11">
+        <v>88</v>
+      </c>
+      <c r="K17" s="11">
+        <v>43</v>
+      </c>
+      <c r="L17" s="11">
+        <v>36</v>
+      </c>
+      <c r="M17" s="11">
+        <v>36</v>
+      </c>
+      <c r="N17" s="11">
+        <v>56</v>
+      </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
       <c r="A18" s="10">
@@ -1510,7 +1620,7 @@
         <v>38</v>
       </c>
       <c r="E18" s="11">
-        <v>32.5</v>
+        <v>33</v>
       </c>
       <c r="F18" s="11">
         <v>50</v>
@@ -1524,11 +1634,21 @@
       <c r="I18" s="11">
         <v>40</v>
       </c>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
+      <c r="J18" s="11">
+        <v>88</v>
+      </c>
+      <c r="K18" s="11">
+        <v>43</v>
+      </c>
+      <c r="L18" s="11">
+        <v>36</v>
+      </c>
+      <c r="M18" s="11">
+        <v>36</v>
+      </c>
+      <c r="N18" s="11">
+        <v>62</v>
+      </c>
     </row>
     <row r="19" spans="1:14" ht="24.95" customHeight="1"/>
     <row r="20" spans="1:14" ht="15" customHeight="1">
@@ -1579,8 +1699,8 @@
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
       <c r="D1" s="30"/>
       <c r="E1" s="30"/>
       <c r="F1" s="30"/>
@@ -1594,40 +1714,40 @@
       <c r="N1" s="30"/>
     </row>
     <row r="2" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="32"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
     </row>
     <row r="3" spans="1:14 16384:16384" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="35"/>
       <c r="C3" s="35"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34"/>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="32"/>
+      <c r="N3" s="32"/>
     </row>
     <row r="4" spans="1:14 16384:16384" ht="24.95" customHeight="1"/>
     <row r="5" spans="1:14 16384:16384" s="1" customFormat="1" ht="36" customHeight="1" thickBot="1">
@@ -1688,7 +1808,7 @@
         <v>38</v>
       </c>
       <c r="E6" s="27">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="F6" s="27">
         <v>50</v>
@@ -1702,11 +1822,21 @@
       <c r="I6" s="27">
         <v>36</v>
       </c>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
+      <c r="J6" s="27">
+        <v>93</v>
+      </c>
+      <c r="K6" s="27">
+        <v>65</v>
+      </c>
+      <c r="L6" s="27">
+        <v>46</v>
+      </c>
+      <c r="M6" s="27">
+        <v>46</v>
+      </c>
+      <c r="N6" s="27">
+        <v>78</v>
+      </c>
     </row>
     <row r="7" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A7" s="10">
@@ -1736,11 +1866,21 @@
       <c r="I7" s="27">
         <v>39</v>
       </c>
-      <c r="J7" s="27"/>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27"/>
-      <c r="N7" s="27"/>
+      <c r="J7" s="27">
+        <v>93</v>
+      </c>
+      <c r="K7" s="27">
+        <v>78</v>
+      </c>
+      <c r="L7" s="27">
+        <v>56</v>
+      </c>
+      <c r="M7" s="27">
+        <v>56</v>
+      </c>
+      <c r="N7" s="27">
+        <v>80</v>
+      </c>
     </row>
     <row r="8" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A8" s="10">
@@ -1759,7 +1899,7 @@
         <v>65</v>
       </c>
       <c r="F8" s="27">
-        <v>77.5</v>
+        <v>78</v>
       </c>
       <c r="G8" s="27">
         <v>26</v>
@@ -1770,11 +1910,21 @@
       <c r="I8" s="27">
         <v>42</v>
       </c>
-      <c r="J8" s="27"/>
-      <c r="K8" s="27"/>
-      <c r="L8" s="27"/>
-      <c r="M8" s="27"/>
-      <c r="N8" s="27"/>
+      <c r="J8" s="27">
+        <v>83</v>
+      </c>
+      <c r="K8" s="27">
+        <v>68</v>
+      </c>
+      <c r="L8" s="27">
+        <v>42</v>
+      </c>
+      <c r="M8" s="27">
+        <v>42</v>
+      </c>
+      <c r="N8" s="27">
+        <v>72</v>
+      </c>
     </row>
     <row r="9" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A9" s="10">
@@ -1804,11 +1954,21 @@
       <c r="I9" s="27">
         <v>23</v>
       </c>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
+      <c r="J9" s="27">
+        <v>93</v>
+      </c>
+      <c r="K9" s="27">
+        <v>55</v>
+      </c>
+      <c r="L9" s="27">
+        <v>32</v>
+      </c>
+      <c r="M9" s="27">
+        <v>32</v>
+      </c>
+      <c r="N9" s="27">
+        <v>76</v>
+      </c>
     </row>
     <row r="10" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A10" s="10">
@@ -1838,11 +1998,21 @@
       <c r="I10" s="27">
         <v>39</v>
       </c>
-      <c r="J10" s="27"/>
-      <c r="K10" s="27"/>
-      <c r="L10" s="27"/>
-      <c r="M10" s="27"/>
-      <c r="N10" s="27"/>
+      <c r="J10" s="27">
+        <v>90</v>
+      </c>
+      <c r="K10" s="27">
+        <v>68</v>
+      </c>
+      <c r="L10" s="27">
+        <v>48</v>
+      </c>
+      <c r="M10" s="27">
+        <v>48</v>
+      </c>
+      <c r="N10" s="27">
+        <v>72</v>
+      </c>
     </row>
     <row r="11" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A11" s="10">
@@ -1858,7 +2028,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="27">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="F11" s="27">
         <v>75</v>
@@ -1872,11 +2042,21 @@
       <c r="I11" s="27">
         <v>25</v>
       </c>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
+      <c r="J11" s="27">
+        <v>90</v>
+      </c>
+      <c r="K11" s="27">
+        <v>60</v>
+      </c>
+      <c r="L11" s="27">
+        <v>52</v>
+      </c>
+      <c r="M11" s="27">
+        <v>52</v>
+      </c>
+      <c r="N11" s="27">
+        <v>82</v>
+      </c>
     </row>
     <row r="12" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A12" s="10">
@@ -1906,11 +2086,21 @@
       <c r="I12" s="27">
         <v>31</v>
       </c>
-      <c r="J12" s="27"/>
-      <c r="K12" s="27"/>
-      <c r="L12" s="27"/>
-      <c r="M12" s="27"/>
-      <c r="N12" s="27"/>
+      <c r="J12" s="27">
+        <v>93</v>
+      </c>
+      <c r="K12" s="27">
+        <v>75</v>
+      </c>
+      <c r="L12" s="27">
+        <v>34</v>
+      </c>
+      <c r="M12" s="27">
+        <v>34</v>
+      </c>
+      <c r="N12" s="27">
+        <v>80</v>
+      </c>
     </row>
     <row r="13" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
       <c r="A13" s="10">
@@ -1929,7 +2119,7 @@
         <v>50</v>
       </c>
       <c r="F13" s="27">
-        <v>67.5</v>
+        <v>68</v>
       </c>
       <c r="G13" s="27">
         <v>36</v>
@@ -1940,11 +2130,21 @@
       <c r="I13" s="27">
         <v>28</v>
       </c>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
+      <c r="J13" s="27">
+        <v>85</v>
+      </c>
+      <c r="K13" s="27">
+        <v>70</v>
+      </c>
+      <c r="L13" s="27">
+        <v>56</v>
+      </c>
+      <c r="M13" s="27">
+        <v>56</v>
+      </c>
+      <c r="N13" s="27">
+        <v>80</v>
+      </c>
     </row>
     <row r="14" spans="1:14 16384:16384" s="1" customFormat="1" ht="18.95" customHeight="1">
       <c r="A14" s="22"/>
@@ -2115,20 +2315,20 @@
       <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
     </row>
     <row r="3" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
     </row>
     <row r="4" spans="1:4" s="1" customFormat="1" ht="24.95" customHeight="1">
       <c r="A4" s="5"/>

--- a/Daftar Nilai Paket B.xlsx
+++ b/Daftar Nilai Paket B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASATIDZ\Zen\Laporan PKBM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF27855F-2552-498C-A78E-08703C51C491}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FADD99B-1764-4112-8EA2-BA4FB8250651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rekap Bangun Rejo" sheetId="1" r:id="rId1"/>
@@ -1133,37 +1133,37 @@
         <v>17</v>
       </c>
       <c r="D7" s="11">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="E7" s="11">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="F7" s="11">
+        <v>91</v>
+      </c>
+      <c r="G7" s="11">
+        <v>100</v>
+      </c>
+      <c r="H7" s="11">
         <v>75</v>
       </c>
-      <c r="G7" s="11">
-        <v>40</v>
-      </c>
-      <c r="H7" s="11">
-        <v>22</v>
-      </c>
       <c r="I7" s="11">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="J7" s="11">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K7" s="11">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="L7" s="11">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="M7" s="11">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="N7" s="11">
-        <v>82</v>
+        <v>97</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1177,37 +1177,37 @@
         <v>18</v>
       </c>
       <c r="D8" s="11">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="E8" s="11">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F8" s="11">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="G8" s="11">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="H8" s="11">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I8" s="11">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="J8" s="11">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K8" s="11">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="L8" s="11">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="M8" s="11">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="N8" s="11">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1221,37 +1221,37 @@
         <v>19</v>
       </c>
       <c r="D9" s="11">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="E9" s="11">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="F9" s="11">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G9" s="11">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="H9" s="11">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I9" s="11">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="J9" s="11">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K9" s="11">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="L9" s="11">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="M9" s="11">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="N9" s="11">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1265,37 +1265,37 @@
         <v>20</v>
       </c>
       <c r="D10" s="11">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="E10" s="11">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="F10" s="11">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G10" s="11">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="H10" s="11">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="I10" s="11">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="J10" s="11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K10" s="11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="L10" s="11">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="M10" s="11">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="N10" s="11">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1309,37 +1309,37 @@
         <v>21</v>
       </c>
       <c r="D11" s="11">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="E11" s="11">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="F11" s="11">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="G11" s="11">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="H11" s="11">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="I11" s="11">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="J11" s="11">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K11" s="11">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L11" s="11">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="M11" s="11">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="N11" s="11">
-        <v>84</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1353,37 +1353,37 @@
         <v>22</v>
       </c>
       <c r="D12" s="11">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="E12" s="11">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="F12" s="11">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="G12" s="11">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="H12" s="11">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="I12" s="11">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="J12" s="11">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K12" s="11">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="L12" s="11">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="M12" s="11">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="N12" s="11">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1397,37 +1397,37 @@
         <v>23</v>
       </c>
       <c r="D13" s="11">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="E13" s="11">
-        <v>53</v>
+        <v>84</v>
       </c>
       <c r="F13" s="11">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="G13" s="11">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="H13" s="11">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="I13" s="11">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="J13" s="11">
         <v>80</v>
       </c>
       <c r="K13" s="11">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="L13" s="11">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="M13" s="11">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="N13" s="11">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1441,37 +1441,37 @@
         <v>24</v>
       </c>
       <c r="D14" s="11">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="E14" s="11">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F14" s="11">
-        <v>65</v>
+        <v>87</v>
       </c>
       <c r="G14" s="11">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="H14" s="11">
-        <v>45</v>
+        <v>92</v>
       </c>
       <c r="I14" s="11">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="J14" s="11">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K14" s="11">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="L14" s="11">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="M14" s="11">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="N14" s="11">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1485,37 +1485,37 @@
         <v>25</v>
       </c>
       <c r="D15" s="11">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E15" s="11">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="F15" s="11">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="G15" s="11">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="H15" s="11">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="I15" s="11">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="J15" s="11">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K15" s="11">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="L15" s="11">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="M15" s="11">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="N15" s="11">
-        <v>78</v>
+        <v>94</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1529,37 +1529,37 @@
         <v>26</v>
       </c>
       <c r="D16" s="11">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E16" s="11">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F16" s="11">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G16" s="11">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="H16" s="11">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="I16" s="11">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="J16" s="11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K16" s="11">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="L16" s="11">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="M16" s="11">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="N16" s="11">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1573,37 +1573,37 @@
         <v>28</v>
       </c>
       <c r="D17" s="11">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="E17" s="11">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="F17" s="11">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G17" s="11">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="H17" s="11">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="I17" s="11">
-        <v>36</v>
+        <v>82</v>
       </c>
       <c r="J17" s="11">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K17" s="11">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="L17" s="11">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="M17" s="11">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="N17" s="11">
-        <v>56</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="30.95" customHeight="1" thickBot="1">
@@ -1617,37 +1617,37 @@
         <v>29</v>
       </c>
       <c r="D18" s="11">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="E18" s="11">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="F18" s="11">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="G18" s="11">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="H18" s="11">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="I18" s="11">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="J18" s="11">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K18" s="11">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="L18" s="11">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="M18" s="11">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="N18" s="11">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="24.95" customHeight="1"/>
@@ -1805,37 +1805,37 @@
         <v>34</v>
       </c>
       <c r="D6" s="27">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="E6" s="27">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="F6" s="27">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="G6" s="27">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="H6" s="27">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="I6" s="27">
-        <v>36</v>
+        <v>92</v>
       </c>
       <c r="J6" s="27">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K6" s="27">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="L6" s="27">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="M6" s="27">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="N6" s="27">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
@@ -1849,37 +1849,37 @@
         <v>36</v>
       </c>
       <c r="D7" s="27">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="E7" s="27">
-        <v>55</v>
+        <v>93</v>
       </c>
       <c r="F7" s="27">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="G7" s="27">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="H7" s="27">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="I7" s="27">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="J7" s="27">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K7" s="27">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="L7" s="27">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="M7" s="27">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="N7" s="27">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="8" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
@@ -1893,37 +1893,37 @@
         <v>37</v>
       </c>
       <c r="D8" s="27">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E8" s="27">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F8" s="27">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="G8" s="27">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="H8" s="27">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="I8" s="27">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="J8" s="27">
         <v>83</v>
       </c>
       <c r="K8" s="27">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="L8" s="27">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="M8" s="27">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="N8" s="27">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
@@ -1937,37 +1937,37 @@
         <v>39</v>
       </c>
       <c r="D9" s="27">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="E9" s="27">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="F9" s="27">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="G9" s="27">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="H9" s="27">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="I9" s="27">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="J9" s="27">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K9" s="27">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="L9" s="27">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="M9" s="27">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="N9" s="27">
-        <v>76</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
@@ -1981,37 +1981,37 @@
         <v>41</v>
       </c>
       <c r="D10" s="27">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E10" s="27">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="F10" s="27">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="G10" s="27">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="H10" s="27">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="I10" s="27">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="J10" s="27">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K10" s="27">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="L10" s="27">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="M10" s="27">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="N10" s="27">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
@@ -2025,37 +2025,37 @@
         <v>43</v>
       </c>
       <c r="D11" s="27">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="E11" s="27">
-        <v>53</v>
+        <v>92</v>
       </c>
       <c r="F11" s="27">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="G11" s="27">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="H11" s="27">
-        <v>43</v>
+        <v>89</v>
       </c>
       <c r="I11" s="27">
-        <v>25</v>
+        <v>77</v>
       </c>
       <c r="J11" s="27">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K11" s="27">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="L11" s="27">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="M11" s="27">
-        <v>52</v>
+        <v>95</v>
       </c>
       <c r="N11" s="27">
-        <v>82</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
@@ -2069,37 +2069,37 @@
         <v>45</v>
       </c>
       <c r="D12" s="27">
-        <v>23</v>
+        <v>75</v>
       </c>
       <c r="E12" s="27">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="F12" s="27">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="G12" s="27">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="H12" s="27">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="I12" s="27">
-        <v>31</v>
+        <v>85</v>
       </c>
       <c r="J12" s="27">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K12" s="27">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="L12" s="27">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="M12" s="27">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="N12" s="27">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:14 16384:16384" s="1" customFormat="1" ht="42.95" customHeight="1" thickBot="1">
@@ -2113,37 +2113,37 @@
         <v>47</v>
       </c>
       <c r="D13" s="27">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="E13" s="27">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="F13" s="27">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="G13" s="27">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="H13" s="27">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="I13" s="27">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="J13" s="27">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" s="27">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="L13" s="27">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="M13" s="27">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="N13" s="27">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:14 16384:16384" s="1" customFormat="1" ht="18.95" customHeight="1">
